--- a/survey_templates/008_mah_jongg_participation_survey--survey_templates.xlsx
+++ b/survey_templates/008_mah_jongg_participation_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1079,8 +1079,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'jubilee'}</t>
+          <t>jubilee</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Jubilee'}</t>
+          <t>Jubilee</t>
         </is>
       </c>
     </row>
@@ -1125,12 +1125,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'jolly'}</t>
+          <t>jolly</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Jolly'}</t>
+          <t>Jolly</t>
         </is>
       </c>
     </row>
@@ -1142,12 +1142,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'jazz'}</t>
+          <t>jazz</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Jazz'}</t>
+          <t>Jazz</t>
         </is>
       </c>
     </row>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'java'}</t>
+          <t>java</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Java'}</t>
+          <t>Java</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'jam'}</t>
+          <t>jam</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Jam'}</t>
+          <t>Jam</t>
         </is>
       </c>
     </row>
@@ -1193,12 +1193,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_"jammin'jazz"}</t>
+          <t>jammin'jazz</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': "Jammin'Jazz"}</t>
+          <t>Jammin'Jazz</t>
         </is>
       </c>
     </row>
@@ -1210,12 +1210,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'mah_jongg'}</t>
+          <t>mah_jongg</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Mah Jongg'}</t>
+          <t>Mah Jongg</t>
         </is>
       </c>
     </row>
@@ -1227,12 +1227,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1244,12 +1244,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'yes'}</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Yes'}</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1261,12 +1261,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'no'}</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'No'}</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1278,12 +1278,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'not_sure'}</t>
+          <t>not_sure</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Not Sure'}</t>
+          <t>Not Sure</t>
         </is>
       </c>
     </row>
@@ -1295,12 +1295,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'other_-_specify'}</t>
+          <t>other_-_specify</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Other - Specify'}</t>
+          <t>Other - Specify</t>
         </is>
       </c>
     </row>
@@ -1312,12 +1312,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'not_applicable'}</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Not Applicable'}</t>
+          <t>Not Applicable</t>
         </is>
       </c>
     </row>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'i_had_fun'}</t>
+          <t>i_had_fun</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'I had fun'}</t>
+          <t>I had fun</t>
         </is>
       </c>
     </row>
@@ -1346,12 +1346,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'i_did_not_have_fun'}</t>
+          <t>i_did_not_have_fun</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'I did not have fun'}</t>
+          <t>I did not have fun</t>
         </is>
       </c>
     </row>
@@ -1363,12 +1363,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'i_had_some_fun'}</t>
+          <t>i_had_some_fun</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'I had some fun'}</t>
+          <t>I had some fun</t>
         </is>
       </c>
     </row>
@@ -1380,12 +1380,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'easy_going'}</t>
+          <t>easy_going</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'Easy going'}</t>
+          <t>Easy going</t>
         </is>
       </c>
     </row>
@@ -1397,12 +1397,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'challenging'}</t>
+          <t>challenging</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'Challenging'}</t>
+          <t>Challenging</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'easy'}</t>
+          <t>easy</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 'Easy'}</t>
+          <t>Easy</t>
         </is>
       </c>
     </row>
@@ -1431,12 +1431,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_'fun'}</t>
+          <t>fun</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 'Fun'}</t>
+          <t>Fun</t>
         </is>
       </c>
     </row>
@@ -1448,12 +1448,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_'easy_going'}</t>
+          <t>easy_going</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': 'Easy going'}</t>
+          <t>Easy going</t>
         </is>
       </c>
     </row>
@@ -1465,12 +1465,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_'challenging'}</t>
+          <t>challenging</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': 'Challenging'}</t>
+          <t>Challenging</t>
         </is>
       </c>
     </row>
@@ -1482,12 +1482,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'value':_'easy'}</t>
+          <t>easy</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'value': 'Easy'}</t>
+          <t>Easy</t>
         </is>
       </c>
     </row>
@@ -1499,12 +1499,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'value':_'fun'}</t>
+          <t>fun</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'value': 'Fun'}</t>
+          <t>Fun</t>
         </is>
       </c>
     </row>
@@ -1516,12 +1516,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'value':_'easy_going'}</t>
+          <t>easy_going</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'value': 'Easy going'}</t>
+          <t>Easy going</t>
         </is>
       </c>
     </row>
@@ -1533,12 +1533,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'value':_'challenging'}</t>
+          <t>challenging</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'value': 'Challenging'}</t>
+          <t>Challenging</t>
         </is>
       </c>
     </row>
@@ -1550,12 +1550,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'value':_'easy'}</t>
+          <t>easy</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'value': 'Easy'}</t>
+          <t>Easy</t>
         </is>
       </c>
     </row>
@@ -1567,12 +1567,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'value':_'fun'}</t>
+          <t>fun</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'value': 'Fun'}</t>
+          <t>Fun</t>
         </is>
       </c>
     </row>
@@ -1584,12 +1584,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'value':_'easy_going'}</t>
+          <t>easy_going</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'value': 'Easy going'}</t>
+          <t>Easy going</t>
         </is>
       </c>
     </row>
@@ -1601,12 +1601,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'value':_'challenging'}</t>
+          <t>challenging</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'value': 'Challenging'}</t>
+          <t>Challenging</t>
         </is>
       </c>
     </row>
@@ -1618,12 +1618,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'value':_'easy'}</t>
+          <t>easy</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'value': 'Easy'}</t>
+          <t>Easy</t>
         </is>
       </c>
     </row>
@@ -1635,12 +1635,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'value':_'fun'}</t>
+          <t>fun</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'value': 'Fun'}</t>
+          <t>Fun</t>
         </is>
       </c>
     </row>
